--- a/regions/hierarchy_withanalysis.xlsx
+++ b/regions/hierarchy_withanalysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melek/Documents/GitHub/Switch-USA-PG-ReEDS/pg/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melek/Documents/GitHub/Switch-USA-PG-ReEDS/regions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79713A8-6613-E040-BE91-B8C0BA0E776C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A2A75D-C0C8-D545-838B-82E65294EDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{34F0B409-DBEE-0442-BCDF-0DA958119CAA}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hierarchy!$A$1:$O$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$1:$C$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$B$1:$S$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$S$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1818,13 +1818,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFC21F52-5999-6E4F-8D62-53494B9D9DE1}" name="Table1" displayName="Table1" ref="A1:C135" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:C135" xr:uid="{EFC21F52-5999-6E4F-8D62-53494B9D9DE1}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="No"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DFE0BB8B-C1CD-404E-80D3-C99BB62741D3}" name="ba"/>
     <tableColumn id="2" xr3:uid="{579BF4FD-FDF1-E245-8732-8D38F37160E6}" name="aggregated?">
@@ -2155,7 +2148,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{976FC11E-5E3D-FB44-A267-86203009BA47}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:O135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -2206,7 +2198,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2253,7 +2245,7 @@
         <v>5332062</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2300,7 +2292,7 @@
         <v>1621289</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -2347,7 +2339,7 @@
         <v>854317</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2394,7 +2386,7 @@
         <v>150512</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -2441,7 +2433,7 @@
         <v>3628310</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -2488,7 +2480,7 @@
         <v>579400</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -2535,7 +2527,7 @@
         <v>64661</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -2582,7 +2574,7 @@
         <v>79329</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -2629,7 +2621,7 @@
         <v>15926605</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -2676,7 +2668,7 @@
         <v>20126530</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -2723,7 +2715,7 @@
         <v>3298799</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -2770,7 +2762,7 @@
         <v>868596</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2817,7 +2809,7 @@
         <v>2398871</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -2864,7 +2856,7 @@
         <v>355602</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -2911,7 +2903,7 @@
         <v>1086448</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2958,7 +2950,7 @@
         <v>559569</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>56</v>
       </c>
@@ -3005,7 +2997,7 @@
         <v>457969</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -3052,7 +3044,7 @@
         <v>410450</v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -3099,7 +3091,7 @@
         <v>8615</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -3146,7 +3138,7 @@
         <v>205121</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -3193,7 +3185,7 @@
         <v>210305</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -3240,7 +3232,7 @@
         <v>41781</v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>68</v>
       </c>
@@ -3287,7 +3279,7 @@
         <v>62587</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -3334,7 +3326,7 @@
         <v>272945</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -3381,7 +3373,7 @@
         <v>3346735</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -3428,7 +3420,7 @@
         <v>156878</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>76</v>
       </c>
@@ -3475,7 +3467,7 @@
         <v>226479</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -3522,7 +3514,7 @@
         <v>6160448</v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>85</v>
       </c>
@@ -3569,7 +3561,7 @@
         <v>64800</v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -3616,7 +3608,7 @@
         <v>1130657</v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -3663,7 +3655,7 @@
         <v>1855700</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -3710,7 +3702,7 @@
         <v>172368</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -3757,7 +3749,7 @@
         <v>4591248</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>99</v>
       </c>
@@ -3804,7 +3796,7 @@
         <v>1366245</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>100</v>
       </c>
@@ -3851,7 +3843,7 @@
         <v>55078</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>106</v>
       </c>
@@ -3898,7 +3890,7 @@
         <v>286406</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>108</v>
       </c>
@@ -3945,7 +3937,7 @@
         <v>510162</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -3992,7 +3984,7 @@
         <v>752301</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>113</v>
       </c>
@@ -4039,7 +4031,7 @@
         <v>99487</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>115</v>
       </c>
@@ -4086,7 +4078,7 @@
         <v>600503</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>116</v>
       </c>
@@ -4133,7 +4125,7 @@
         <v>1305475</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -4180,7 +4172,7 @@
         <v>260630</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>121</v>
       </c>
@@ -4227,7 +4219,7 @@
         <v>5068222</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>122</v>
       </c>
@@ -4274,7 +4266,7 @@
         <v>137794</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>123</v>
       </c>
@@ -4321,7 +4313,7 @@
         <v>697822</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>126</v>
       </c>
@@ -4368,7 +4360,7 @@
         <v>848915</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>129</v>
       </c>
@@ -4415,7 +4407,7 @@
         <v>274556</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>133</v>
       </c>
@@ -4462,7 +4454,7 @@
         <v>887914</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -4509,7 +4501,7 @@
         <v>27735</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>140</v>
       </c>
@@ -4556,7 +4548,7 @@
         <v>2698218</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>141</v>
       </c>
@@ -4603,7 +4595,7 @@
         <v>1369440</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>142</v>
       </c>
@@ -4650,7 +4642,7 @@
         <v>112050</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>144</v>
       </c>
@@ -4697,7 +4689,7 @@
         <v>2858556</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>145</v>
       </c>
@@ -4744,7 +4736,7 @@
         <v>1660454</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>147</v>
       </c>
@@ -4791,7 +4783,7 @@
         <v>1009019</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>148</v>
       </c>
@@ -4838,7 +4830,7 @@
         <v>1065175</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>152</v>
       </c>
@@ -4885,7 +4877,7 @@
         <v>452334</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>153</v>
       </c>
@@ -4932,7 +4924,7 @@
         <v>4265849</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>156</v>
       </c>
@@ -4979,7 +4971,7 @@
         <v>875784</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>159</v>
       </c>
@@ -5026,7 +5018,7 @@
         <v>158359</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>163</v>
       </c>
@@ -5073,7 +5065,7 @@
         <v>420687</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>164</v>
       </c>
@@ -5120,7 +5112,7 @@
         <v>408192</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>165</v>
       </c>
@@ -5167,7 +5159,7 @@
         <v>10930571</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>166</v>
       </c>
@@ -5214,7 +5206,7 @@
         <v>3859594</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>167</v>
       </c>
@@ -5261,7 +5253,7 @@
         <v>4958269</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>168</v>
       </c>
@@ -5308,7 +5300,7 @@
         <v>1590760</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>169</v>
       </c>
@@ -5355,7 +5347,7 @@
         <v>6748367</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>170</v>
       </c>
@@ -5402,7 +5394,7 @@
         <v>326505</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>171</v>
       </c>
@@ -5449,7 +5441,7 @@
         <v>321679</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>172</v>
       </c>
@@ -5496,7 +5488,7 @@
         <v>2221987</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>173</v>
       </c>
@@ -5543,7 +5535,7 @@
         <v>123559</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>175</v>
       </c>
@@ -5590,7 +5582,7 @@
         <v>2898404</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>176</v>
       </c>
@@ -5637,7 +5629,7 @@
         <v>184836</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>177</v>
       </c>
@@ -5684,7 +5676,7 @@
         <v>242527</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>179</v>
       </c>
@@ -5731,7 +5723,7 @@
         <v>824494</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>180</v>
       </c>
@@ -5778,7 +5770,7 @@
         <v>952149</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>181</v>
       </c>
@@ -5825,7 +5817,7 @@
         <v>291964</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>182</v>
       </c>
@@ -5872,7 +5864,7 @@
         <v>790991</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>183</v>
       </c>
@@ -5919,7 +5911,7 @@
         <v>2252462</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>184</v>
       </c>
@@ -5966,7 +5958,7 @@
         <v>9489127</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>188</v>
       </c>
@@ -6013,7 +6005,7 @@
         <v>1713915</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>189</v>
       </c>
@@ -6060,7 +6052,7 @@
         <v>581156</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>190</v>
       </c>
@@ -6107,7 +6099,7 @@
         <v>925960</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>191</v>
       </c>
@@ -6154,7 +6146,7 @@
         <v>369194</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>192</v>
       </c>
@@ -6201,7 +6193,7 @@
         <v>2023179</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>193</v>
       </c>
@@ -6248,7 +6240,7 @@
         <v>331891</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>194</v>
       </c>
@@ -6295,7 +6287,7 @@
         <v>2288217</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>197</v>
       </c>
@@ -6342,7 +6334,7 @@
         <v>654828</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>201</v>
       </c>
@@ -6389,7 +6381,7 @@
         <v>2624318</v>
       </c>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>207</v>
       </c>
@@ -6436,7 +6428,7 @@
         <v>2533381</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>209</v>
       </c>
@@ -6483,7 +6475,7 @@
         <v>1174308</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>213</v>
       </c>
@@ -6530,7 +6522,7 @@
         <v>7227750</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>216</v>
       </c>
@@ -6577,7 +6569,7 @@
         <v>704418</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>219</v>
       </c>
@@ -6624,7 +6616,7 @@
         <v>11180878</v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>221</v>
       </c>
@@ -6671,7 +6663,7 @@
         <v>2074483</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>225</v>
       </c>
@@ -6718,7 +6710,7 @@
         <v>3404348</v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>227</v>
       </c>
@@ -6765,7 +6757,7 @@
         <v>5567260</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>229</v>
       </c>
@@ -6812,7 +6804,7 @@
         <v>5478764</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>231</v>
       </c>
@@ -6859,7 +6851,7 @@
         <v>7364395</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>234</v>
       </c>
@@ -6906,7 +6898,7 @@
         <v>251129</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>235</v>
       </c>
@@ -6953,7 +6945,7 @@
         <v>14352997</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>239</v>
       </c>
@@ -7000,7 +6992,7 @@
         <v>7844910</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>241</v>
       </c>
@@ -7047,7 +7039,7 @@
         <v>9291599</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>242</v>
       </c>
@@ -7094,7 +7086,7 @@
         <v>606333</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>243</v>
       </c>
@@ -7141,7 +7133,7 @@
         <v>3656917</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>245</v>
       </c>
@@ -7188,7 +7180,7 @@
         <v>1361332</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>246</v>
       </c>
@@ -7235,7 +7227,7 @@
         <v>1906026</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>247</v>
       </c>
@@ -7282,7 +7274,7 @@
         <v>362350</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>248</v>
       </c>
@@ -7329,7 +7321,7 @@
         <v>3248424</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>249</v>
       </c>
@@ -7376,7 +7368,7 @@
         <v>273180</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>250</v>
       </c>
@@ -7423,7 +7415,7 @@
         <v>4547881</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>252</v>
       </c>
@@ -7470,7 +7462,7 @@
         <v>4470190</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>253</v>
       </c>
@@ -7517,7 +7509,7 @@
         <v>1113858</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>254</v>
       </c>
@@ -7564,7 +7556,7 @@
         <v>1751375</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>255</v>
       </c>
@@ -7611,7 +7603,7 @@
         <v>2379644</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>259</v>
       </c>
@@ -7658,7 +7650,7 @@
         <v>1087399</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>261</v>
       </c>
@@ -7705,7 +7697,7 @@
         <v>682580</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>262</v>
       </c>
@@ -7752,7 +7744,7 @@
         <v>1150256</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>263</v>
       </c>
@@ -7799,7 +7791,7 @@
         <v>248135</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>265</v>
       </c>
@@ -7846,7 +7838,7 @@
         <v>173737</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>266</v>
       </c>
@@ -7893,7 +7885,7 @@
         <v>552035</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>268</v>
       </c>
@@ -7940,7 +7932,7 @@
         <v>10277235</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>269</v>
       </c>
@@ -7987,7 +7979,7 @@
         <v>6413435</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>270</v>
       </c>
@@ -8034,7 +8026,7 @@
         <v>45415</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>271</v>
       </c>
@@ -8081,7 +8073,7 @@
         <v>1051917</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>273</v>
       </c>
@@ -8128,7 +8120,7 @@
         <v>9500851</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>275</v>
       </c>
@@ -8175,7 +8167,7 @@
         <v>16938901</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>280</v>
       </c>
@@ -8222,7 +8214,7 @@
         <v>2928347</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>281</v>
       </c>
@@ -8269,7 +8261,7 @@
         <v>648493</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>287</v>
       </c>
@@ -8316,7 +8308,7 @@
         <v>1409032</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>289</v>
       </c>
@@ -8363,7 +8355,7 @@
         <v>7136171</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>291</v>
       </c>
@@ -8457,7 +8449,7 @@
         <v>1112308</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>295</v>
       </c>
@@ -8505,13 +8497,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O135" xr:uid="{976FC11E-5E3D-FB44-A267-86203009BA47}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="p133"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O135" xr:uid="{976FC11E-5E3D-FB44-A267-86203009BA47}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12101,11 +12087,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:S47" xr:uid="{EFD0705F-0649-0746-87F5-4B967309B5E1}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:S47">
-      <sortCondition descending="1" ref="H1:H47"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12194,7 +12175,7 @@
         <v>population</v>
       </c>
     </row>
-    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -12270,7 +12251,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -12283,7 +12264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -12296,7 +12277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -12309,7 +12290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -12322,7 +12303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -12335,7 +12316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -12348,7 +12329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -12361,7 +12342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -12374,7 +12355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -12387,7 +12368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -12400,7 +12381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -12413,7 +12394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -12426,7 +12407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -12439,7 +12420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -12452,7 +12433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -12465,7 +12446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>56</v>
       </c>
@@ -12478,7 +12459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -12491,7 +12472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -12504,7 +12485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -12517,7 +12498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -12530,7 +12511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -12543,7 +12524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>68</v>
       </c>
@@ -12556,7 +12537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -12569,7 +12550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -12582,7 +12563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -12595,7 +12576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>76</v>
       </c>
@@ -12608,7 +12589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -12621,7 +12602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>85</v>
       </c>
@@ -12634,7 +12615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -12647,7 +12628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -12660,7 +12641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -12673,7 +12654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -12686,7 +12667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>99</v>
       </c>
@@ -12699,7 +12680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>100</v>
       </c>
@@ -12712,7 +12693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>106</v>
       </c>
@@ -12725,7 +12706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>108</v>
       </c>
@@ -12738,7 +12719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -12751,7 +12732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>113</v>
       </c>
@@ -12764,7 +12745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>115</v>
       </c>
@@ -12777,7 +12758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>116</v>
       </c>
@@ -12790,7 +12771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -12803,7 +12784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>121</v>
       </c>
@@ -12816,7 +12797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>122</v>
       </c>
@@ -12829,7 +12810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>123</v>
       </c>
@@ -12842,7 +12823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>126</v>
       </c>
@@ -12855,7 +12836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>129</v>
       </c>
@@ -12868,7 +12849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>133</v>
       </c>
@@ -12881,7 +12862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -12894,7 +12875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>140</v>
       </c>
@@ -12907,7 +12888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>141</v>
       </c>
@@ -12920,7 +12901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>142</v>
       </c>
@@ -12933,7 +12914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>144</v>
       </c>
@@ -12946,7 +12927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>145</v>
       </c>
@@ -12959,7 +12940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>147</v>
       </c>
@@ -12972,7 +12953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>148</v>
       </c>
@@ -12985,7 +12966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>152</v>
       </c>
@@ -12998,7 +12979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>153</v>
       </c>
@@ -13011,7 +12992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>156</v>
       </c>
@@ -13024,7 +13005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>159</v>
       </c>
@@ -13037,7 +13018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>163</v>
       </c>
@@ -13050,7 +13031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>164</v>
       </c>
@@ -13063,7 +13044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>165</v>
       </c>
@@ -13076,7 +13057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>166</v>
       </c>
@@ -13089,7 +13070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>167</v>
       </c>
@@ -13102,7 +13083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>168</v>
       </c>
@@ -13115,7 +13096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>169</v>
       </c>
@@ -13128,7 +13109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>170</v>
       </c>
@@ -13141,7 +13122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>171</v>
       </c>
@@ -13154,7 +13135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>172</v>
       </c>
@@ -13167,7 +13148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>173</v>
       </c>
@@ -13180,7 +13161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>175</v>
       </c>
@@ -13193,7 +13174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>176</v>
       </c>
@@ -13206,7 +13187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>177</v>
       </c>
@@ -13219,7 +13200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>179</v>
       </c>
@@ -13232,7 +13213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>180</v>
       </c>
@@ -13245,7 +13226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>181</v>
       </c>
@@ -13258,7 +13239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>182</v>
       </c>
@@ -13271,7 +13252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>183</v>
       </c>
@@ -13284,7 +13265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>184</v>
       </c>
@@ -13297,7 +13278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>188</v>
       </c>
@@ -13310,7 +13291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>189</v>
       </c>
@@ -13323,7 +13304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>190</v>
       </c>
@@ -13336,7 +13317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>191</v>
       </c>
@@ -13349,7 +13330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>192</v>
       </c>
@@ -13362,7 +13343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>193</v>
       </c>
@@ -13375,7 +13356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>194</v>
       </c>
@@ -13388,7 +13369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>197</v>
       </c>
@@ -13401,7 +13382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>201</v>
       </c>
@@ -13414,7 +13395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>207</v>
       </c>
@@ -13427,7 +13408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>209</v>
       </c>
@@ -13440,7 +13421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>213</v>
       </c>
@@ -13453,7 +13434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>216</v>
       </c>
@@ -13466,7 +13447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>219</v>
       </c>
@@ -13479,7 +13460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>221</v>
       </c>
@@ -13492,7 +13473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>225</v>
       </c>
@@ -13505,7 +13486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>227</v>
       </c>
@@ -13518,7 +13499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>229</v>
       </c>
@@ -13531,7 +13512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>231</v>
       </c>
@@ -13544,7 +13525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>234</v>
       </c>
@@ -13557,7 +13538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>235</v>
       </c>
@@ -13570,7 +13551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>239</v>
       </c>
@@ -13583,7 +13564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>241</v>
       </c>
@@ -13596,7 +13577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>242</v>
       </c>
@@ -13609,7 +13590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>243</v>
       </c>
@@ -13622,7 +13603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>245</v>
       </c>
@@ -13635,7 +13616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>246</v>
       </c>
@@ -13648,7 +13629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>247</v>
       </c>
@@ -13661,7 +13642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>248</v>
       </c>
@@ -13674,7 +13655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>249</v>
       </c>
@@ -13687,7 +13668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>250</v>
       </c>
@@ -13700,7 +13681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>252</v>
       </c>
@@ -13713,7 +13694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>253</v>
       </c>
@@ -13726,7 +13707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>254</v>
       </c>
@@ -13739,7 +13720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>255</v>
       </c>
@@ -13765,7 +13746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>261</v>
       </c>
@@ -13778,7 +13759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>262</v>
       </c>
@@ -13791,7 +13772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>263</v>
       </c>
@@ -13804,7 +13785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>265</v>
       </c>
@@ -13817,7 +13798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>266</v>
       </c>
@@ -13830,7 +13811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>268</v>
       </c>
@@ -13843,7 +13824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>269</v>
       </c>
@@ -13856,7 +13837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>270</v>
       </c>
@@ -13869,7 +13850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>271</v>
       </c>
@@ -13882,7 +13863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>273</v>
       </c>
@@ -13895,7 +13876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>275</v>
       </c>
@@ -13908,7 +13889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>280</v>
       </c>
@@ -13921,7 +13902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>281</v>
       </c>
@@ -13934,7 +13915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>287</v>
       </c>
@@ -13947,7 +13928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>289</v>
       </c>
@@ -13960,7 +13941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>291</v>
       </c>
@@ -13986,7 +13967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>295</v>
       </c>
